--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>16/08 13:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>200</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>16/08 18:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>80</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>16/08 13:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>22/08 23:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>15/08 15:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>50</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>17/08 19:15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>15/08 00:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>50</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>17/08 19:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>14/08 17:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>35</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>16/08 13:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>40</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>17/08 17:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>16/08 15:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>17/08 19:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>55</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>16/08 15:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>55</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>16/08 23:05</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>50</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>16/08 00:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>15/08 18:45</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
+      <c r="F23" t="n">
+        <v>3.45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>23/08 23:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45883.07762133906</v>
+        <v>45883.07762134259</v>
       </c>
     </row>
     <row r="25">
@@ -1540,23 +1494,156 @@
           <t>17/08 19:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+6,58%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45883.07762134259</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Jeonbuk Mo</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors – Daegu FCK League 1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>16/08 10:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>+6,58%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>45883.07762133906</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+7,65%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45883.14043096087</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Burgos CF </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Burgos CF – Cultural LeonesaLaLiga2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>15/08 19:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+7,12%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45883.14043096087</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 1.5 - break1er participant | Lucia Bron</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lucia Bronzetti – Cori GauffWTA - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Moins que 1.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>14/08 15:05</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>50,5%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+6,01%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45883.14043096087</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -1537,10 +1537,8 @@
           <t>16/08 10:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1553,7 +1551,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45883.14043096087</v>
+        <v>45883.14043096065</v>
       </c>
     </row>
     <row r="27">
@@ -1582,10 +1580,8 @@
           <t>15/08 19:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>50</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1598,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45883.14043096087</v>
+        <v>45883.14043096065</v>
       </c>
     </row>
     <row r="28">
@@ -1627,10 +1623,8 @@
           <t>14/08 15:05</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1643,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45883.14043096087</v>
+        <v>45883.14043096065</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1640,6 +1640,51 @@
         <v>45883.14043096065</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Alianza FC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar – Once CaldasPrimera A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>15/08 21:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+6,50%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45883.22442797828</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>15/08 21:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>45</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,187 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45883.22442797828</v>
+        <v>45883.22442797454</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 11.5 - tirs1re équipe | Nice – Tou</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nice – ToulouseFrance - Ligue 1 McDonald’s®</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16/08 19:05</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>37,7%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+20,5%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45883.27439815102</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fluminense</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fluminense – FortalezaSérie A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>16/08 19:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+20,3%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45883.27439815102</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 27.5 - tirs | Lens – Lyo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Lens – LyonFrance - Ligue 1 McDonald’s®</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moins que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>16/08 15:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>62,8%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+18,1%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45883.27439815102</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Aston Vill</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Aston Villa – NewcastleAngleterre - Angl. Premier League (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>16/08 11:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>47,6%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+9,40%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45883.27439815102</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>16/08 19:05</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F30" t="n">
+        <v>3.2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45883.27439815102</v>
+        <v>45883.27439814815</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>16/08 19:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>60</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45883.27439815102</v>
+        <v>45883.27439814815</v>
       </c>
     </row>
     <row r="32">
@@ -1799,10 +1795,8 @@
           <t>16/08 15:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
+      <c r="F32" t="n">
+        <v>1.88</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1815,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45883.27439815102</v>
+        <v>45883.27439814815</v>
       </c>
     </row>
     <row r="33">
@@ -1844,10 +1838,8 @@
           <t>16/08 11:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2.3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1860,7 +1852,232 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45883.27439815102</v>
+        <v>45883.27439814815</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Central Có</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Central Córdoba – Atletico LanusInternational - Copa Sudamericana - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>15/08 00:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+42,9%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45883.30796162765</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tirs2e équipe | Atletico M</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – Godoy CruzInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>14/08 22:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>47,7%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+31,2%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45883.30796162765</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré1re équipe | Universita</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes – PalmeirasInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>15/08 00:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>26,3%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+18,5%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45883.30796162765</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 14.5 - tirs1re équipe | Monaco – L</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Monaco – Le HavreFrance - Ligue 1 McDonald’s®</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 14.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16/08 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+14,3%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45883.30796162765</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Huracan</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CA Huracan – Argentinos JuniorsLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>16/08 19:15</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+10,8%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45883.30796162765</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>15/08 00:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F34" t="n">
+        <v>3.2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45883.30796162765</v>
+        <v>45883.30796163194</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>14/08 22:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.75</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45883.30796162765</v>
+        <v>45883.30796163194</v>
       </c>
     </row>
     <row r="36">
@@ -1971,10 +1967,8 @@
           <t>15/08 00:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F36" t="n">
+        <v>4.5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1987,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45883.30796162765</v>
+        <v>45883.30796163194</v>
       </c>
     </row>
     <row r="37">
@@ -2016,10 +2010,8 @@
           <t>16/08 17:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2032,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45883.30796162765</v>
+        <v>45883.30796163194</v>
       </c>
     </row>
     <row r="38">
@@ -2061,10 +2053,8 @@
           <t>16/08 19:15</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>60</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2077,7 +2067,187 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45883.30796162765</v>
+        <v>45883.30796163194</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football | 1 / ANB | SV Atlas D</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SV Atlas Delmenhorst – Borussia MönchengladbachAllemagne - Coupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1 / ANB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>17/08 13:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+42,3%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45883.35530819478</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Majorque –</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Majorque – BarceloneEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>16/08 17:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+27,9%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45883.35530819478</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 7.5 - tirs2e équipe | Tottenham </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tottenham – BurnleyAngleterre - Angl. Premier League</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16/08 14:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+25,4%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45883.35530819478</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 26.5 - tirs | Wolverhamp</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wolverhampton – Manchester CityAngleterre - Angl. Premier League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>16/08 16:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>61,9%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45883.35530819478</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45883.35530819478</v>
+        <v>45883.35530819444</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>16/08 17:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F40" t="n">
+        <v>3.1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45883.35530819478</v>
+        <v>45883.35530819444</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>16/08 14:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F41" t="n">
+        <v>3.4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45883.35530819478</v>
+        <v>45883.35530819444</v>
       </c>
     </row>
     <row r="42">
@@ -2231,10 +2225,8 @@
           <t>16/08 16:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F42" t="n">
+        <v>1.8</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2247,7 +2239,142 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45883.35530819478</v>
+        <v>45883.35530819444</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Noah – </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FC Noah – Lincoln Red Imps FCLigue Europa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>14/08 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+34,3%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45883.39367757139</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 27.5 - tirs | Majorque –</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Majorque – BarceloneEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Moins que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>16/08 17:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>62,1%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+16,7%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45883.39367757139</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | E.Seidel –</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>E.Seidel – V.GrachevaWTA - Cincinnati F</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>14/08 19:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>49,3%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45883.39367757139</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>14/08 17:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>60</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45883.39367757139</v>
+        <v>45883.39367756945</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>16/08 17:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
+      <c r="F44" t="n">
+        <v>1.88</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45883.39367757139</v>
+        <v>45883.39367756945</v>
       </c>
     </row>
     <row r="45">
@@ -2358,10 +2354,8 @@
           <t>14/08 19:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2.25</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2374,7 +2368,52 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45883.39367757139</v>
+        <v>45883.39367756945</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 19.5 - tirs | Wolfsberge</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wolfsberger AC – PAOK SaloniqueEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Moins que 19.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>14/08 17:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+17,8%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45883.4345496647</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>14/08 17:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F46" t="n">
+        <v>3.2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,52 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45883.4345496647</v>
+        <v>45883.43454966435</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Deportivo </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira – America de CaliPrimera A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>14/08 23:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+40,3%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45883.47215367571</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>14/08 23:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>60</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,142 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45883.47215367571</v>
+        <v>45883.47215368056</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 19.5 - tirs | Wolfsberge</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Wolfsberger AC – PAOK SaloniqueLigue Europa</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Moins que 19.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>14/08 17:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+24,4%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45883.53409370252</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Spartak Tr</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Spartak Trnava – CS Universitatea CraiovaEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>14/08 18:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>35,8%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+14,6%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45883.53409370252</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 11.5 - tirs1re équipe | Valence – </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Valence – Real SociedadEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>16/08 19:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45883.53409370252</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>14/08 17:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.9</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45883.53409370252</v>
+        <v>45883.5340937037</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>14/08 18:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F49" t="n">
+        <v>3.2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45883.53409370252</v>
+        <v>45883.5340937037</v>
       </c>
     </row>
     <row r="50">
@@ -2573,10 +2569,8 @@
           <t>16/08 19:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.7</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2589,7 +2583,187 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45883.53409370252</v>
+        <v>45883.5340937037</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 9.5 - tirs2e équipe | Wolfsberge</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wolfsberger AC – PAOK SaloniqueLigue Europa</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>14/08 17:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+22,0%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45883.56776660577</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 27.5 - tirs | Spartak Tr</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Spartak Trnava – Universitatea CraiovaLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>14/08 18:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+17,7%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45883.56776660577</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 22.5 - tirs | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – PanathinaikosEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>14/08 18:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+15,5%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45883.56776660577</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | Pas de buts | JK Tallinn</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JK Tallinna Kalev – Levadia TallinnEstonie. Estonie - Premier League</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>17/08 16:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45883.56776660577</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>14/08 17:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.55</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45883.56776660577</v>
+        <v>45883.56776660879</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>14/08 18:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F52" t="n">
+        <v>3.2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45883.56776660577</v>
+        <v>45883.56776660879</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>14/08 18:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F53" t="n">
+        <v>2.75</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45883.56776660577</v>
+        <v>45883.56776660879</v>
       </c>
     </row>
     <row r="54">
@@ -2747,10 +2741,8 @@
           <t>17/08 16:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>55</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2763,7 +2755,277 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45883.56776660577</v>
+        <v>45883.56776660879</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 15.5 - tirs2e équipe | Majorque –</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Majorque – FC BarceloneLaLiga</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moins que 15.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>16/08 17:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>46,7%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+28,3%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45883.5991652567</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 24.5 - tirs | Aston Vill</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Aston Villa – NewcastlePremier League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>16/08 11:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>43,4%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+25,9%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45883.5991652567</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 24.5 - tirs | Lens – Lyo</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lens – LyonLigue 1 McDonald's®</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>16/08 15:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+21,8%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45883.5991652567</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 23.5 - tirs | Wolverhamp</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wolverhampton – Manchester CityPremier League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>16/08 16:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+19,1%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45883.5991652567</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 24.5 - tirs | Brighton –</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Brighton – FulhamPremier League</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>16/08 14:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+13,7%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45883.5991652567</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 11.5 - tirs1re équipe | Nice – Tou</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Nice – ToulouseLigue 1 McDonald's®</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>16/08 19:05</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>36,6%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+13,5%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45883.5991652567</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>16/08 17:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.75</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45883.5991652567</v>
+        <v>45883.59916525463</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>16/08 11:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F56" t="n">
+        <v>2.9</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45883.5991652567</v>
+        <v>45883.59916525463</v>
       </c>
     </row>
     <row r="57">
@@ -2874,10 +2870,8 @@
           <t>16/08 15:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F57" t="n">
+        <v>2.95</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2890,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45883.5991652567</v>
+        <v>45883.59916525463</v>
       </c>
     </row>
     <row r="58">
@@ -2919,10 +2913,8 @@
           <t>16/08 16:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F58" t="n">
+        <v>2.95</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2935,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45883.5991652567</v>
+        <v>45883.59916525463</v>
       </c>
     </row>
     <row r="59">
@@ -2964,10 +2956,8 @@
           <t>16/08 14:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.65</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2980,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45883.5991652567</v>
+        <v>45883.59916525463</v>
       </c>
     </row>
     <row r="60">
@@ -3009,10 +2999,8 @@
           <t>16/08 19:05</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3025,7 +3013,97 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45883.5991652567</v>
+        <v>45883.59916525463</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football | 1 / ANB | RSV Eintra</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>RSV Eintracht 1949 – FC KaiserslauternAllemagne - Coupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1 / ANB</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>17/08 13:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>33,8%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+14,8%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45883.64236826252</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 21.5 - tirs | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – Panathinaïkos FCEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 21.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>14/08 18:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+12,1%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45883.64236826252</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F61" t="n">
+        <v>3.4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45883.64236826252</v>
+        <v>45883.64236826389</v>
       </c>
     </row>
     <row r="62">
@@ -3087,23 +3085,111 @@
           <t>14/08 18:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+12,1%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45883.64236826389</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Atletico M</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – Godoy CruzInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>14/08 22:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>35,0%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>+12,1%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>45883.64236826252</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+14,4%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45883.68746069863</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 6.5 - tir cadré1re équipe | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – AEK LarnacaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 6.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>14/08 19:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>30,6%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+13,1%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45883.68746069863</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>14/08 22:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F63" t="n">
+        <v>3.2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45883.68746069863</v>
+        <v>45883.68746069445</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>14/08 19:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F64" t="n">
+        <v>3.7</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,232 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45883.68746069863</v>
+        <v>45883.68746069445</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 21.5 - tirs | Braga – CF</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Braga – CFR Cluj385076e7 Europe - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Moins que 21.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>14/08 18:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+59,3%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45883.72249830199</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tirs2e équipe | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – AEK LarnacaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>14/08 19:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+38,0%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45883.72249830199</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Union Sant</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Union Santa Fe – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>24/08 17:15</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+22,5%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45883.72249830199</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cadix – Mi</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cadix – MirandesLaLiga2</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>17/08 17:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+19,3%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45883.72249830199</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 24.5 - tirs | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – Panathinaïkos FCEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>14/08 18:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>59,0%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+18,0%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45883.72249830199</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>14/08 18:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F65" t="n">
+        <v>3.25</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45883.72249830199</v>
+        <v>45883.72249829861</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>14/08 19:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F66" t="n">
+        <v>3.3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45883.72249830199</v>
+        <v>45883.72249829861</v>
       </c>
     </row>
     <row r="67">
@@ -3304,10 +3300,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>55</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3320,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45883.72249830199</v>
+        <v>45883.72249829861</v>
       </c>
     </row>
     <row r="68">
@@ -3349,10 +3343,8 @@
           <t>17/08 17:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>55</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3365,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45883.72249830199</v>
+        <v>45883.72249829861</v>
       </c>
     </row>
     <row r="69">
@@ -3394,10 +3386,8 @@
           <t>14/08 18:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>2</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3410,7 +3400,52 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45883.72249830199</v>
+        <v>45883.72249829861</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 7.5 - tirs2e équipe | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – AEK LarnacaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>14/08 19:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+43,6%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45883.77333532144</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3429,10 +3429,8 @@
           <t>14/08 19:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F70" t="n">
+        <v>3.25</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3445,7 +3443,52 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45883.77333532144</v>
+        <v>45883.77333532408</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Central Co</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Central Cordoba – Atletico LanusCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>15/08 00:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+13,4%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45883.80454906712</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>15/08 00:30</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>65</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,52 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45883.80454906712</v>
+        <v>45883.8045490625</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Botafogo – Liga Deportiva UniversitariaInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>14/08 22:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>24,2%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+9,05%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45883.85141017454</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>14/08 22:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F72" t="n">
+        <v>4.5</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,52 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45883.85141017454</v>
+        <v>45883.85141017361</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | A.Rublev –</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>A.Rublev – C.AlcarazATP - Cincinnati H</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>15/08 15:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>67,5%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+7,95%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45883.88958923913</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,10 +3558,8 @@
           <t>15/08 15:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F73" t="n">
+        <v>1.6</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3574,7 +3572,97 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45883.88958923913</v>
+        <v>45883.88958923611</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Universita</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Universitario de Deportes – PalmeirasCopa Libertadores</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>15/08 00:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,70%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+10,6%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45883.93174174073</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Platens</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CA Platense – San LorenzoLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>16/08 17:15</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+9,73%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45883.93174174073</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-14.xlsx
+++ b/data/valuebets_database_2025-08-14.xlsx
@@ -3601,10 +3601,8 @@
           <t>15/08 00:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>65</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3617,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45883.93174174073</v>
+        <v>45883.93174173611</v>
       </c>
     </row>
     <row r="75">
@@ -3646,10 +3644,8 @@
           <t>16/08 17:15</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>45</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3662,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45883.93174174073</v>
+        <v>45883.93174173611</v>
       </c>
     </row>
   </sheetData>
